--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487D53EE-A432-467C-B5D0-D1A048A21047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D785DF4-F663-4DE0-98DF-27DF7E26A03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="231">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -310,10 +310,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LED 전류 설정 (1mA 단위 조절)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수행할 명령 코드, "2. Command 목록" 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -904,32 +900,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10ms delay</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 필요</t>
-    </r>
+    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 10ms delay 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 ~ 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 전류 Amplitude 설정 (1mA 단위 조절)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 전류 Duty 설정 (1% 단위 조절)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -940,9 +931,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="&quot;B-&quot;0"/>
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
-    <numFmt numFmtId="180" formatCode="0.000&quot;mA&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.000&quot;mA&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,15 +999,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1671,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1700,9 +1682,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,6 +1955,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1988,85 +1979,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2104,14 +2080,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>31433</xdr:rowOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>28258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2154,7 +2130,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2225,7 +2201,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2298,14 +2274,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>31432</xdr:rowOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>28258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2348,7 +2324,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2419,7 +2395,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2492,13 +2468,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2549,13 +2525,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2606,7 +2582,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2689,7 +2665,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2772,14 +2748,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>31431</xdr:rowOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>28256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2822,7 +2798,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2893,7 +2869,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2966,13 +2942,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3023,13 +2999,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3080,7 +3056,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3163,7 +3139,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3791,7 +3767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P109"/>
+  <dimension ref="B2:P110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3813,14 +3789,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="102" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
+      <c r="B3" s="105" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3872,14 +3848,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3891,14 +3867,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="108" t="s">
+      <c r="E8" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="108"/>
-      <c r="G8" s="108"/>
-      <c r="H8" s="108"/>
-      <c r="I8" s="108"/>
-      <c r="J8" s="108"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3910,14 +3886,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="105"/>
+      <c r="E9" s="106" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="108"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3929,33 +3905,33 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="108" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="108"/>
-      <c r="G10" s="108"/>
-      <c r="H10" s="108"/>
-      <c r="I10" s="108"/>
-      <c r="J10" s="108"/>
+      <c r="E10" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="128" t="s">
+      <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="125" t="s">
-        <v>215</v>
-      </c>
-      <c r="F11" s="126"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
+      <c r="E11" s="106" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="108"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3967,14 +3943,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="108" t="s">
+      <c r="E12" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3986,18 +3962,18 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="103" t="s">
+      <c r="E13" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.45">
@@ -4013,13 +3989,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="103"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4034,13 +4010,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="108" t="s">
-        <v>204</v>
-      </c>
-      <c r="G18" s="108"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="108"/>
+      <c r="F18" s="102" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="102"/>
+      <c r="J18" s="102"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4055,34 +4031,34 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="108" t="s">
-        <v>199</v>
-      </c>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
+      <c r="F19" s="102" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="102"/>
+      <c r="J19" s="102"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="102" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="G20" s="108"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="108"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="102"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4097,13 +4073,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="108"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="108"/>
+      <c r="F21" s="126" t="s">
+        <v>229</v>
+      </c>
+      <c r="G21" s="126"/>
+      <c r="H21" s="126"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="126"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4112,19 +4088,19 @@
       <c r="C22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="128" t="s">
+      <c r="D22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="129" t="s">
-        <v>216</v>
-      </c>
-      <c r="G22" s="129"/>
-      <c r="H22" s="129"/>
-      <c r="I22" s="129"/>
-      <c r="J22" s="129"/>
+      <c r="F22" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="G22" s="102"/>
+      <c r="H22" s="102"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="102"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4133,19 +4109,19 @@
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="128" t="s">
+      <c r="D23" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="129" t="s">
-        <v>217</v>
-      </c>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="129"/>
+      <c r="F23" s="102" t="s">
+        <v>216</v>
+      </c>
+      <c r="G23" s="102"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="102"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4154,19 +4130,19 @@
       <c r="C24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="128" t="s">
+      <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="129" t="s">
-        <v>218</v>
-      </c>
-      <c r="G24" s="129"/>
-      <c r="H24" s="129"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="129"/>
+        <v>120</v>
+      </c>
+      <c r="F24" s="102" t="s">
+        <v>217</v>
+      </c>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="102"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4175,209 +4151,214 @@
       <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="128" t="s">
+      <c r="D25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="129" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="102" t="s">
+        <v>218</v>
+      </c>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="102"/>
+      <c r="J25" s="102"/>
+      <c r="L25" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="M25" s="101" t="s">
         <v>219</v>
       </c>
-      <c r="G25" s="129"/>
-      <c r="H25" s="129"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="129"/>
-      <c r="L25" s="130" t="s">
+      <c r="N25" s="101" t="s">
         <v>222</v>
       </c>
-      <c r="M25" s="130" t="s">
+      <c r="O25" s="101" t="s">
+        <v>224</v>
+      </c>
+      <c r="P25" s="101" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F26" s="102" t="s">
         <v>220</v>
       </c>
-      <c r="N25" s="130" t="s">
-        <v>223</v>
-      </c>
-      <c r="O25" s="130" t="s">
-        <v>225</v>
-      </c>
-      <c r="P25" s="130" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B26" s="128" t="s">
-        <v>212</v>
-      </c>
-      <c r="C26" s="128" t="s">
-        <v>213</v>
-      </c>
-      <c r="D26" s="128" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="128" t="s">
-        <v>214</v>
-      </c>
-      <c r="F26" s="129" t="s">
-        <v>221</v>
-      </c>
-      <c r="G26" s="129"/>
-      <c r="H26" s="129"/>
-      <c r="I26" s="129"/>
-      <c r="J26" s="129"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
-      <c r="M26" s="131">
+      <c r="M26" s="128">
         <f>L26/4095*128</f>
         <v>25.006105006105006</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="129">
         <v>20</v>
       </c>
-      <c r="O26" s="132">
+      <c r="O26" s="130">
         <f>N26/16383</f>
         <v>1.2207776353537203E-3</v>
       </c>
-      <c r="P26" s="131">
+      <c r="P26" s="128">
         <f>M26*O26</f>
         <v>3.0526893738759699E-2</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B29" s="5" t="s">
-        <v>210</v>
-      </c>
+      <c r="B27" s="127" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="127" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="127" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="127" t="s">
+        <v>228</v>
+      </c>
+      <c r="F27" s="126" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="125"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="125"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B31" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="7" t="s">
+      <c r="C31" s="9"/>
+      <c r="D31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="107" t="s">
+      <c r="E31" s="10"/>
+      <c r="F31" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="G30" s="107"/>
-      <c r="H30" s="107"/>
-      <c r="I30" s="107"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="107"/>
-      <c r="M30" s="107"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B31" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="M31" s="17" t="s">
-        <v>122</v>
-      </c>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B33" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="19" t="s">
+      <c r="E33" s="17"/>
+      <c r="F33" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="G33" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H33" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="I32" s="20" t="s">
+      <c r="I33" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="J32" s="21" t="s">
+      <c r="J33" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="K32" s="20" t="s">
+      <c r="K33" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L33" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M32" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B33" s="8" t="s">
+      <c r="M33" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B34" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B34" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
@@ -4388,15 +4369,15 @@
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -4407,13 +4388,15 @@
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B36" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C36" s="12"/>
+        <v>29</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="D36" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -4424,15 +4407,13 @@
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B37" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C37" s="11"/>
       <c r="D37" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -4443,15 +4424,15 @@
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -4462,15 +4443,15 @@
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B39" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -4481,15 +4462,15 @@
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -4500,15 +4481,15 @@
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B41" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -4519,31 +4500,55 @@
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B44" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B45" s="6" t="s">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B42" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B45" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B46" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B78" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B77" s="6" t="s">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B110" s="6" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B109" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F30:M30"/>
+    <mergeCell ref="F31:M31"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="E12:J12"/>
@@ -4555,11 +4560,7 @@
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F26:J26"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F27:J27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4580,888 +4581,888 @@
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="109" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="107" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="107" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="104" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="110"/>
-      <c r="D3" s="107"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="I3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="L3" s="28" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B4" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="27" t="s">
+      <c r="B4" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="23">
         <v>1</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="24">
         <f t="shared" ref="F4:L13" si="0">E4+20</f>
         <v>21</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="24">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="24">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="24">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="24">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="24">
         <f t="shared" ref="K4:K23" si="1">J4+20</f>
         <v>121</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="25">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B5" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="23">
         <v>2</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="24">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="24">
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="24">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="24">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
-      <c r="L5" s="26">
+      <c r="L5" s="25">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="B6" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <v>3</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="24">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="24">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="24">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="24">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="24">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="24">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="25">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="27" t="s">
+      <c r="B7" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <v>4</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="24">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="24">
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="24">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="25">
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B8" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="27" t="s">
+      <c r="B8" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="23">
         <v>5</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="24">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="24">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="24">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="25">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="B9" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="D9" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="23">
         <v>6</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="24">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="24">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="24">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="24">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="25">
         <f t="shared" si="0"/>
         <v>146</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="B10" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="24">
+      <c r="D10" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="23">
         <v>7</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="24">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="24">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="24">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="24">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="24">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="24">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="25">
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="B11" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="24">
+      <c r="D11" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="23">
         <v>8</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="24">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="24">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="24">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="24">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="24">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="25">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="27" t="s">
+      <c r="B12" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="24">
+      <c r="D12" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="23">
         <v>9</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="24">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="24">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="24">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="25">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B13" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="27" t="s">
+      <c r="B13" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="24">
+      <c r="D13" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="23">
         <v>10</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="24">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="25">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B14" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="27" t="s">
+      <c r="B14" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="24">
+      <c r="D14" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="23">
         <v>11</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <f t="shared" ref="F14:L23" si="2">E14+20</f>
         <v>31</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="24">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="24">
         <f t="shared" si="1"/>
         <v>131</v>
       </c>
-      <c r="L14" s="26">
+      <c r="L14" s="25">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B15" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="B15" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="24">
+      <c r="D15" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="23">
         <v>12</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="24">
         <f t="shared" si="1"/>
         <v>132</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="25">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B16" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="27" t="s">
+      <c r="B16" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="24">
+      <c r="D16" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="23">
         <v>13</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="24">
         <f t="shared" si="1"/>
         <v>133</v>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="25">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B17" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="B17" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="24">
+      <c r="D17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="23">
         <v>14</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="24">
         <f t="shared" si="1"/>
         <v>134</v>
       </c>
-      <c r="L17" s="26">
+      <c r="L17" s="25">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="27" t="s">
+      <c r="B18" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="24">
+      <c r="D18" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="23">
         <v>15</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="24">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="24">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="24">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="24">
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="24">
         <f t="shared" si="1"/>
         <v>135</v>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="25">
         <f t="shared" si="2"/>
         <v>155</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B19" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="27" t="s">
+      <c r="B19" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="24">
+      <c r="D19" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="23">
         <v>16</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <f t="shared" si="2"/>
         <v>56</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="24">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="24">
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="24">
         <f t="shared" si="1"/>
         <v>136</v>
       </c>
-      <c r="L19" s="26">
+      <c r="L19" s="25">
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="27" t="s">
+      <c r="B20" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="23">
         <v>17</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <f t="shared" si="2"/>
         <v>57</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="24">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="24">
         <f t="shared" si="1"/>
         <v>137</v>
       </c>
-      <c r="L20" s="26">
+      <c r="L20" s="25">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B21" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="27" t="s">
+      <c r="B21" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="23">
         <v>18</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="24">
         <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="24">
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="24">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="24">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="24">
         <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="L21" s="26">
+      <c r="L21" s="25">
         <f t="shared" si="2"/>
         <v>158</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="27" t="s">
+      <c r="B22" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="23">
         <v>19</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="24">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="24">
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="24">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="24">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="24">
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="24">
         <f t="shared" si="1"/>
         <v>139</v>
       </c>
-      <c r="L22" s="26">
+      <c r="L22" s="25">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B23" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="27" t="s">
+      <c r="B23" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="D23" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="23">
         <v>20</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="24">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="24">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="24">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="24">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="24">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="24">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="L23" s="26">
+      <c r="L23" s="25">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
@@ -5484,243 +5485,243 @@
   <dimension ref="B1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.58203125" style="29" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.75" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.08203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.58203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.75" style="29" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="29"/>
-    <col min="14" max="14" width="9.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="29"/>
+    <col min="1" max="1" width="2.58203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.08203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.75" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="28"/>
+    <col min="14" max="14" width="9.25" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" s="57">
+        <v>1</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="44"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" s="58">
+        <v>2</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" s="52"/>
+      <c r="L4" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" s="58">
+        <v>3</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="52"/>
+      <c r="L5" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" s="58">
+        <v>4</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="47"/>
+      <c r="G6" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="55" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" s="58">
+        <v>5</v>
+      </c>
+      <c r="C7" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="39" t="s">
+      <c r="D7" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="L7" s="55" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="59">
+        <v>6</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="100" t="s">
+        <v>204</v>
+      </c>
+      <c r="H8" s="30" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="58">
-        <v>1</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="45"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="55" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B4" s="59">
-        <v>2</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="48" t="s">
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="56" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="G4" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B5" s="59">
-        <v>3</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="I5" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="K5" s="53"/>
-      <c r="L5" s="56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" s="59">
-        <v>4</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="48"/>
-      <c r="G6" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="H6" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" s="59">
-        <v>5</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="K7" s="53" t="s">
-        <v>203</v>
-      </c>
-      <c r="L7" s="56" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="60">
-        <v>6</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="101" t="s">
-        <v>205</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="57" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" s="29" t="s">
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B11" s="28" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="29" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -5745,13 +5746,13 @@
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" t="s">
         <v>166</v>
       </c>
-      <c r="H2" t="s">
+      <c r="W2" t="s">
         <v>167</v>
-      </c>
-      <c r="W2" t="s">
-        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -5778,151 +5779,151 @@
   <sheetData>
     <row r="2" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="114" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C3" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="119" t="s">
-        <v>173</v>
-      </c>
       <c r="F3" s="114" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="117"/>
       <c r="H3" s="117"/>
       <c r="I3" s="117"/>
       <c r="J3" s="117" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K3" s="117"/>
       <c r="L3" s="117"/>
-      <c r="M3" s="122"/>
+      <c r="M3" s="121"/>
       <c r="N3" s="111" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B4" s="115"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="120"/>
-      <c r="F4" s="61" t="s">
+      <c r="C4" s="104"/>
+      <c r="D4" s="119"/>
+      <c r="F4" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="J4" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="M4" s="73" t="s">
-        <v>116</v>
-      </c>
       <c r="N4" s="112"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="116"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="121"/>
-      <c r="F5" s="71">
+      <c r="B5" s="122"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="124"/>
+      <c r="F5" s="70">
         <v>1</v>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="71">
         <f t="shared" ref="G5:M5" si="0">F5+20</f>
         <v>21</v>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="71">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="71">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="71">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="71">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="L5" s="72">
+      <c r="L5" s="71">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="M5" s="74">
+      <c r="M5" s="73">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
       <c r="N5" s="113"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B6" s="67">
+      <c r="B6" s="66">
         <v>1</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="69">
-        <v>0</v>
-      </c>
-      <c r="F6" s="67">
-        <v>0</v>
-      </c>
-      <c r="G6" s="20">
-        <v>0</v>
-      </c>
-      <c r="H6" s="20">
-        <v>0</v>
-      </c>
-      <c r="I6" s="20">
-        <v>0</v>
-      </c>
-      <c r="J6" s="20">
-        <v>0</v>
-      </c>
-      <c r="K6" s="20">
-        <v>0</v>
-      </c>
-      <c r="L6" s="20">
-        <v>0</v>
-      </c>
-      <c r="M6" s="19">
-        <v>0</v>
-      </c>
-      <c r="N6" s="77" t="s">
-        <v>177</v>
+      <c r="D6" s="68">
+        <v>0</v>
+      </c>
+      <c r="F6" s="66">
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0</v>
+      </c>
+      <c r="N6" s="76" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B7" s="62">
+      <c r="B7" s="61">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="63">
+        <v>173</v>
+      </c>
+      <c r="D7" s="62">
         <v>50</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="61">
         <v>0</v>
       </c>
       <c r="G7" s="8">
@@ -5943,138 +5944,138 @@
       <c r="L7" s="8">
         <v>0</v>
       </c>
-      <c r="M7" s="75">
-        <v>0</v>
-      </c>
-      <c r="N7" s="78" t="s">
-        <v>176</v>
+      <c r="M7" s="74">
+        <v>0</v>
+      </c>
+      <c r="N7" s="77" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B8" s="62">
+      <c r="B8" s="61">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="62">
         <v>1</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="79">
         <v>50</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="80">
         <v>50</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="80">
         <v>50</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="80">
         <v>50</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="80">
         <v>50</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="80">
         <v>50</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="80">
         <v>50</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="81">
         <v>50</v>
       </c>
-      <c r="N8" s="78" t="s">
-        <v>178</v>
+      <c r="N8" s="77" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B9" s="62">
+      <c r="B9" s="61">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="62">
         <v>1</v>
       </c>
-      <c r="F9" s="62">
-        <v>0</v>
-      </c>
-      <c r="G9" s="81">
+      <c r="F9" s="61">
+        <v>0</v>
+      </c>
+      <c r="G9" s="80">
         <v>50</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="80">
         <v>50</v>
       </c>
-      <c r="I9" s="81">
+      <c r="I9" s="80">
         <v>50</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="80">
         <v>50</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="80">
         <v>50</v>
       </c>
-      <c r="L9" s="81">
+      <c r="L9" s="80">
         <v>50</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="81">
         <v>50</v>
       </c>
-      <c r="N9" s="78" t="s">
-        <v>179</v>
+      <c r="N9" s="77" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B10" s="62">
+      <c r="B10" s="61">
         <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="62">
         <v>61</v>
       </c>
-      <c r="F10" s="62">
-        <v>0</v>
-      </c>
-      <c r="G10" s="81">
+      <c r="F10" s="61">
+        <v>0</v>
+      </c>
+      <c r="G10" s="80">
         <v>50</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="80">
         <v>50</v>
       </c>
       <c r="I10" s="8">
         <v>0</v>
       </c>
-      <c r="J10" s="81">
+      <c r="J10" s="80">
         <v>50</v>
       </c>
-      <c r="K10" s="81">
+      <c r="K10" s="80">
         <v>50</v>
       </c>
-      <c r="L10" s="81">
+      <c r="L10" s="80">
         <v>50</v>
       </c>
-      <c r="M10" s="82">
+      <c r="M10" s="81">
         <v>50</v>
       </c>
-      <c r="N10" s="78" t="s">
-        <v>180</v>
+      <c r="N10" s="77" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B11" s="62">
+      <c r="B11" s="61">
         <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="63">
-        <v>0</v>
-      </c>
-      <c r="F11" s="62">
+      <c r="D11" s="62">
+        <v>0</v>
+      </c>
+      <c r="F11" s="61">
         <v>0</v>
       </c>
       <c r="G11" s="8">
@@ -6095,24 +6096,24 @@
       <c r="L11" s="8">
         <v>0</v>
       </c>
-      <c r="M11" s="75">
-        <v>0</v>
-      </c>
-      <c r="N11" s="78" t="s">
-        <v>181</v>
+      <c r="M11" s="74">
+        <v>0</v>
+      </c>
+      <c r="N11" s="77" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B12" s="62">
+      <c r="B12" s="61">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="62">
         <v>81</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="61">
         <v>0</v>
       </c>
       <c r="G12" s="8">
@@ -6124,7 +6125,7 @@
       <c r="I12" s="8">
         <v>0</v>
       </c>
-      <c r="J12" s="81">
+      <c r="J12" s="80">
         <v>50</v>
       </c>
       <c r="K12" s="8">
@@ -6133,274 +6134,274 @@
       <c r="L12" s="8">
         <v>0</v>
       </c>
-      <c r="M12" s="75">
-        <v>0</v>
-      </c>
-      <c r="N12" s="78" t="s">
-        <v>182</v>
+      <c r="M12" s="74">
+        <v>0</v>
+      </c>
+      <c r="N12" s="77" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B13" s="62">
+      <c r="B13" s="61">
         <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="62">
+        <v>100</v>
+      </c>
+      <c r="F13" s="61">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="83">
+        <v>100</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="74">
+        <v>0</v>
+      </c>
+      <c r="N13" s="77" t="s">
         <v>174</v>
       </c>
-      <c r="D13" s="63">
-        <v>100</v>
-      </c>
-      <c r="F13" s="62">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="84">
-        <v>100</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="75">
-        <v>0</v>
-      </c>
-      <c r="N13" s="78" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B14" s="62">
+      <c r="B14" s="61">
         <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="63">
-        <v>0</v>
-      </c>
-      <c r="F14" s="83">
+      <c r="D14" s="62">
+        <v>0</v>
+      </c>
+      <c r="F14" s="82">
         <v>100</v>
       </c>
-      <c r="G14" s="84">
+      <c r="G14" s="83">
         <v>100</v>
       </c>
-      <c r="H14" s="84">
+      <c r="H14" s="83">
         <v>100</v>
       </c>
-      <c r="I14" s="84">
+      <c r="I14" s="83">
         <v>100</v>
       </c>
-      <c r="J14" s="84">
+      <c r="J14" s="83">
         <v>100</v>
       </c>
-      <c r="K14" s="84">
+      <c r="K14" s="83">
         <v>100</v>
       </c>
-      <c r="L14" s="84">
+      <c r="L14" s="83">
         <v>100</v>
       </c>
-      <c r="M14" s="85">
+      <c r="M14" s="84">
         <v>100</v>
       </c>
-      <c r="N14" s="78" t="s">
+      <c r="N14" s="77" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B15" s="63">
+        <v>10</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="65">
+        <v>0</v>
+      </c>
+      <c r="F15" s="63">
+        <v>0</v>
+      </c>
+      <c r="G15" s="69">
+        <v>0</v>
+      </c>
+      <c r="H15" s="69">
+        <v>0</v>
+      </c>
+      <c r="I15" s="69">
+        <v>0</v>
+      </c>
+      <c r="J15" s="69">
+        <v>0</v>
+      </c>
+      <c r="K15" s="69">
+        <v>0</v>
+      </c>
+      <c r="L15" s="69">
+        <v>0</v>
+      </c>
+      <c r="M15" s="75">
+        <v>0</v>
+      </c>
+      <c r="N15" s="78" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="64">
-        <v>10</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="66">
-        <v>0</v>
-      </c>
-      <c r="F15" s="64">
-        <v>0</v>
-      </c>
-      <c r="G15" s="70">
-        <v>0</v>
-      </c>
-      <c r="H15" s="70">
-        <v>0</v>
-      </c>
-      <c r="I15" s="70">
-        <v>0</v>
-      </c>
-      <c r="J15" s="70">
-        <v>0</v>
-      </c>
-      <c r="K15" s="70">
-        <v>0</v>
-      </c>
-      <c r="L15" s="70">
-        <v>0</v>
-      </c>
-      <c r="M15" s="76">
-        <v>0</v>
-      </c>
-      <c r="N15" s="79" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" s="114" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="117" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="119" t="s">
-        <v>173</v>
-      </c>
       <c r="F19" s="114" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G19" s="117"/>
       <c r="H19" s="117"/>
       <c r="I19" s="117"/>
       <c r="J19" s="117" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="117"/>
       <c r="L19" s="117"/>
-      <c r="M19" s="122"/>
+      <c r="M19" s="121"/>
       <c r="N19" s="111" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="115"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="120"/>
-      <c r="F20" s="61" t="s">
+      <c r="C20" s="104"/>
+      <c r="D20" s="119"/>
+      <c r="F20" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="J20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K20" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="L20" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="M20" s="73" t="s">
-        <v>116</v>
-      </c>
       <c r="N20" s="112"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="123"/>
+      <c r="B21" s="116"/>
       <c r="C21" s="109"/>
-      <c r="D21" s="124"/>
-      <c r="F21" s="91">
+      <c r="D21" s="120"/>
+      <c r="F21" s="90">
         <v>12</v>
       </c>
-      <c r="G21" s="92">
+      <c r="G21" s="91">
         <f t="shared" ref="G21" si="1">F21+20</f>
         <v>32</v>
       </c>
-      <c r="H21" s="92">
+      <c r="H21" s="91">
         <f t="shared" ref="H21" si="2">G21+20</f>
         <v>52</v>
       </c>
-      <c r="I21" s="92">
+      <c r="I21" s="91">
         <f t="shared" ref="I21" si="3">H21+20</f>
         <v>72</v>
       </c>
-      <c r="J21" s="92">
+      <c r="J21" s="91">
         <f t="shared" ref="J21" si="4">I21+20</f>
         <v>92</v>
       </c>
-      <c r="K21" s="92">
+      <c r="K21" s="91">
         <f t="shared" ref="K21" si="5">J21+20</f>
         <v>112</v>
       </c>
-      <c r="L21" s="92">
+      <c r="L21" s="91">
         <f t="shared" ref="L21" si="6">K21+20</f>
         <v>132</v>
       </c>
-      <c r="M21" s="93">
+      <c r="M21" s="92">
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
       <c r="N21" s="113"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B22" s="86">
+      <c r="B22" s="85">
         <v>1</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="88">
-        <v>0</v>
-      </c>
-      <c r="F22" s="86">
-        <v>0</v>
-      </c>
-      <c r="G22" s="95">
-        <v>0</v>
-      </c>
-      <c r="H22" s="95">
-        <v>0</v>
-      </c>
-      <c r="I22" s="95">
-        <v>0</v>
-      </c>
-      <c r="J22" s="95">
-        <v>0</v>
-      </c>
-      <c r="K22" s="95">
-        <v>0</v>
-      </c>
-      <c r="L22" s="95">
-        <v>0</v>
-      </c>
-      <c r="M22" s="88">
-        <v>0</v>
-      </c>
-      <c r="N22" s="89" t="s">
-        <v>177</v>
+      <c r="D22" s="87">
+        <v>0</v>
+      </c>
+      <c r="F22" s="85">
+        <v>0</v>
+      </c>
+      <c r="G22" s="94">
+        <v>0</v>
+      </c>
+      <c r="H22" s="94">
+        <v>0</v>
+      </c>
+      <c r="I22" s="94">
+        <v>0</v>
+      </c>
+      <c r="J22" s="94">
+        <v>0</v>
+      </c>
+      <c r="K22" s="94">
+        <v>0</v>
+      </c>
+      <c r="L22" s="94">
+        <v>0</v>
+      </c>
+      <c r="M22" s="87">
+        <v>0</v>
+      </c>
+      <c r="N22" s="88" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B23" s="62">
+      <c r="B23" s="61">
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D23" s="63">
+        <v>173</v>
+      </c>
+      <c r="D23" s="62">
         <v>25</v>
       </c>
-      <c r="F23" s="62">
+      <c r="F23" s="61">
         <v>0</v>
       </c>
       <c r="G23" s="8">
@@ -6421,214 +6422,214 @@
       <c r="L23" s="8">
         <v>0</v>
       </c>
-      <c r="M23" s="63">
-        <v>0</v>
-      </c>
-      <c r="N23" s="90" t="s">
-        <v>187</v>
+      <c r="M23" s="62">
+        <v>0</v>
+      </c>
+      <c r="N23" s="89" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B24" s="62">
+      <c r="B24" s="61">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="63">
+      <c r="D24" s="62">
         <v>12</v>
       </c>
-      <c r="F24" s="80">
+      <c r="F24" s="79">
         <v>25</v>
       </c>
-      <c r="G24" s="81">
+      <c r="G24" s="80">
         <v>25</v>
       </c>
-      <c r="H24" s="81">
+      <c r="H24" s="80">
         <v>25</v>
       </c>
-      <c r="I24" s="81">
+      <c r="I24" s="80">
         <v>25</v>
       </c>
-      <c r="J24" s="81">
+      <c r="J24" s="80">
         <v>25</v>
       </c>
-      <c r="K24" s="81">
+      <c r="K24" s="80">
         <v>25</v>
       </c>
-      <c r="L24" s="81">
+      <c r="L24" s="80">
         <v>25</v>
       </c>
-      <c r="M24" s="96">
+      <c r="M24" s="95">
         <v>25</v>
       </c>
-      <c r="N24" s="90" t="s">
-        <v>188</v>
+      <c r="N24" s="89" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B25" s="62">
+      <c r="B25" s="61">
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="63">
+      <c r="D25" s="62">
         <v>12</v>
       </c>
-      <c r="F25" s="62">
-        <v>0</v>
-      </c>
-      <c r="G25" s="81">
+      <c r="F25" s="61">
+        <v>0</v>
+      </c>
+      <c r="G25" s="80">
         <v>25</v>
       </c>
-      <c r="H25" s="81">
+      <c r="H25" s="80">
         <v>25</v>
       </c>
-      <c r="I25" s="81">
+      <c r="I25" s="80">
         <v>25</v>
       </c>
-      <c r="J25" s="81">
+      <c r="J25" s="80">
         <v>25</v>
       </c>
-      <c r="K25" s="81">
+      <c r="K25" s="80">
         <v>25</v>
       </c>
-      <c r="L25" s="81">
+      <c r="L25" s="80">
         <v>25</v>
       </c>
-      <c r="M25" s="96">
+      <c r="M25" s="95">
         <v>25</v>
       </c>
-      <c r="N25" s="90" t="s">
-        <v>189</v>
+      <c r="N25" s="89" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B26" s="62">
+      <c r="B26" s="61">
         <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="63">
+      <c r="D26" s="62">
         <v>52</v>
       </c>
-      <c r="F26" s="62">
-        <v>0</v>
-      </c>
-      <c r="G26" s="81">
+      <c r="F26" s="61">
+        <v>0</v>
+      </c>
+      <c r="G26" s="80">
         <v>25</v>
       </c>
       <c r="H26" s="8">
         <v>0</v>
       </c>
-      <c r="I26" s="81">
+      <c r="I26" s="80">
         <v>25</v>
       </c>
-      <c r="J26" s="81">
+      <c r="J26" s="80">
         <v>25</v>
       </c>
-      <c r="K26" s="81">
+      <c r="K26" s="80">
         <v>25</v>
       </c>
-      <c r="L26" s="81">
+      <c r="L26" s="80">
         <v>25</v>
       </c>
-      <c r="M26" s="96">
+      <c r="M26" s="95">
         <v>25</v>
       </c>
-      <c r="N26" s="90" t="s">
-        <v>190</v>
+      <c r="N26" s="89" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B27" s="62">
+      <c r="B27" s="61">
         <v>6</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="63">
+      <c r="D27" s="62">
         <v>92</v>
       </c>
-      <c r="F27" s="62">
-        <v>0</v>
-      </c>
-      <c r="G27" s="81">
+      <c r="F27" s="61">
+        <v>0</v>
+      </c>
+      <c r="G27" s="80">
         <v>25</v>
       </c>
       <c r="H27" s="8">
         <v>0</v>
       </c>
-      <c r="I27" s="81">
+      <c r="I27" s="80">
         <v>25</v>
       </c>
       <c r="J27" s="8">
         <v>0</v>
       </c>
-      <c r="K27" s="81">
+      <c r="K27" s="80">
         <v>25</v>
       </c>
-      <c r="L27" s="81">
+      <c r="L27" s="80">
         <v>25</v>
       </c>
-      <c r="M27" s="96">
+      <c r="M27" s="95">
         <v>25</v>
       </c>
-      <c r="N27" s="90" t="s">
-        <v>191</v>
+      <c r="N27" s="89" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B28" s="62">
+      <c r="B28" s="61">
         <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="63">
+      <c r="D28" s="62">
         <v>132</v>
       </c>
-      <c r="F28" s="62">
-        <v>0</v>
-      </c>
-      <c r="G28" s="81">
+      <c r="F28" s="61">
+        <v>0</v>
+      </c>
+      <c r="G28" s="80">
         <v>25</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
       </c>
-      <c r="I28" s="81">
+      <c r="I28" s="80">
         <v>25</v>
       </c>
       <c r="J28" s="8">
         <v>0</v>
       </c>
-      <c r="K28" s="81">
+      <c r="K28" s="80">
         <v>25</v>
       </c>
       <c r="L28" s="8">
         <v>0</v>
       </c>
-      <c r="M28" s="96">
+      <c r="M28" s="95">
         <v>25</v>
       </c>
-      <c r="N28" s="90" t="s">
-        <v>193</v>
+      <c r="N28" s="89" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B29" s="62">
+      <c r="B29" s="61">
         <v>8</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="63">
+      <c r="D29" s="62">
         <v>12</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="61">
         <v>0</v>
       </c>
       <c r="G29" s="8">
@@ -6649,24 +6650,24 @@
       <c r="L29" s="8">
         <v>0</v>
       </c>
-      <c r="M29" s="63">
-        <v>0</v>
-      </c>
-      <c r="N29" s="90" t="s">
-        <v>192</v>
+      <c r="M29" s="62">
+        <v>0</v>
+      </c>
+      <c r="N29" s="89" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B30" s="62">
+      <c r="B30" s="61">
         <v>9</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D30" s="63">
+        <v>173</v>
+      </c>
+      <c r="D30" s="62">
         <v>75</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F30" s="61">
         <v>0</v>
       </c>
       <c r="G30" s="8">
@@ -6687,24 +6688,24 @@
       <c r="L30" s="8">
         <v>0</v>
       </c>
-      <c r="M30" s="63">
-        <v>0</v>
-      </c>
-      <c r="N30" s="90" t="s">
-        <v>194</v>
+      <c r="M30" s="62">
+        <v>0</v>
+      </c>
+      <c r="N30" s="89" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B31" s="62">
+      <c r="B31" s="61">
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="63">
+      <c r="D31" s="62">
         <v>12</v>
       </c>
-      <c r="F31" s="97">
+      <c r="F31" s="96">
         <v>75</v>
       </c>
       <c r="G31" s="8">
@@ -6725,30 +6726,30 @@
       <c r="L31" s="8">
         <v>0</v>
       </c>
-      <c r="M31" s="63">
-        <v>0</v>
-      </c>
-      <c r="N31" s="90" t="s">
-        <v>195</v>
+      <c r="M31" s="62">
+        <v>0</v>
+      </c>
+      <c r="N31" s="89" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B32" s="62">
+      <c r="B32" s="61">
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="63">
+      <c r="D32" s="62">
         <v>52</v>
       </c>
-      <c r="F32" s="97">
+      <c r="F32" s="96">
         <v>75</v>
       </c>
       <c r="G32" s="8">
         <v>0</v>
       </c>
-      <c r="H32" s="94">
+      <c r="H32" s="93">
         <v>75</v>
       </c>
       <c r="I32" s="8">
@@ -6763,36 +6764,36 @@
       <c r="L32" s="8">
         <v>0</v>
       </c>
-      <c r="M32" s="63">
-        <v>0</v>
-      </c>
-      <c r="N32" s="90" t="s">
-        <v>196</v>
+      <c r="M32" s="62">
+        <v>0</v>
+      </c>
+      <c r="N32" s="89" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B33" s="62">
+      <c r="B33" s="61">
         <v>12</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="62">
         <v>92</v>
       </c>
-      <c r="F33" s="97">
+      <c r="F33" s="96">
         <v>75</v>
       </c>
       <c r="G33" s="8">
         <v>0</v>
       </c>
-      <c r="H33" s="94">
+      <c r="H33" s="93">
         <v>75</v>
       </c>
       <c r="I33" s="8">
         <v>0</v>
       </c>
-      <c r="J33" s="94">
+      <c r="J33" s="93">
         <v>75</v>
       </c>
       <c r="K33" s="8">
@@ -6801,65 +6802,65 @@
       <c r="L33" s="8">
         <v>0</v>
       </c>
-      <c r="M33" s="63">
-        <v>0</v>
-      </c>
-      <c r="N33" s="90" t="s">
+      <c r="M33" s="62">
+        <v>0</v>
+      </c>
+      <c r="N33" s="89" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B34" s="63">
+        <v>13</v>
+      </c>
+      <c r="C34" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="65">
+        <v>132</v>
+      </c>
+      <c r="F34" s="97">
+        <v>75</v>
+      </c>
+      <c r="G34" s="69">
+        <v>0</v>
+      </c>
+      <c r="H34" s="98">
+        <v>75</v>
+      </c>
+      <c r="I34" s="69">
+        <v>0</v>
+      </c>
+      <c r="J34" s="98">
+        <v>75</v>
+      </c>
+      <c r="K34" s="69">
+        <v>0</v>
+      </c>
+      <c r="L34" s="98">
+        <v>75</v>
+      </c>
+      <c r="M34" s="65">
+        <v>0</v>
+      </c>
+      <c r="N34" s="99" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B34" s="64">
-        <v>13</v>
-      </c>
-      <c r="C34" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="66">
-        <v>132</v>
-      </c>
-      <c r="F34" s="98">
-        <v>75</v>
-      </c>
-      <c r="G34" s="70">
-        <v>0</v>
-      </c>
-      <c r="H34" s="99">
-        <v>75</v>
-      </c>
-      <c r="I34" s="70">
-        <v>0</v>
-      </c>
-      <c r="J34" s="99">
-        <v>75</v>
-      </c>
-      <c r="K34" s="70">
-        <v>0</v>
-      </c>
-      <c r="L34" s="99">
-        <v>75</v>
-      </c>
-      <c r="M34" s="66">
-        <v>0</v>
-      </c>
-      <c r="N34" s="100" t="s">
-        <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D785DF4-F663-4DE0-98DF-27DF7E26A03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3256A65-BFEA-4D43-B402-BF7FE6B8567C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1958,91 +1958,88 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3848,14 +3845,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="103" t="s">
+      <c r="E7" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="103"/>
-      <c r="J7" s="103"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="109"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3867,14 +3864,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="102" t="s">
+      <c r="E8" s="110" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3905,14 +3902,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3943,14 +3940,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3989,13 +3986,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="103" t="s">
+      <c r="F17" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4010,13 +4007,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="110" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="102"/>
-      <c r="J18" s="102"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4031,13 +4028,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="102" t="s">
+      <c r="F19" s="110" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="102"/>
-      <c r="I19" s="102"/>
-      <c r="J19" s="102"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4052,13 +4049,13 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="102" t="s">
+      <c r="F20" s="110" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="J20" s="102"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4073,13 +4070,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="126" t="s">
+      <c r="F21" s="129" t="s">
         <v>229</v>
       </c>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="126"/>
-      <c r="J21" s="126"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="129"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4094,13 +4091,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="102" t="s">
+      <c r="F22" s="110" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="102"/>
-      <c r="H22" s="102"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="102"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4115,13 +4112,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="102" t="s">
+      <c r="F23" s="110" t="s">
         <v>216</v>
       </c>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="102"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4136,13 +4133,13 @@
       <c r="E24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F24" s="102" t="s">
+      <c r="F24" s="110" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4157,13 +4154,13 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="102" t="s">
+      <c r="F25" s="110" t="s">
         <v>218</v>
       </c>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="102"/>
-      <c r="J25" s="102"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
       <c r="L25" s="101" t="s">
         <v>221</v>
       </c>
@@ -4193,63 +4190,52 @@
       <c r="E26" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F26" s="102" t="s">
+      <c r="F26" s="110" t="s">
         <v>220</v>
       </c>
-      <c r="G26" s="102"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="J26" s="102"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
-      <c r="M26" s="128">
+      <c r="M26" s="103">
         <f>L26/4095*128</f>
         <v>25.006105006105006</v>
       </c>
-      <c r="N26" s="129">
+      <c r="N26" s="6">
         <v>20</v>
       </c>
-      <c r="O26" s="130">
+      <c r="O26" s="104">
         <f>N26/16383</f>
         <v>1.2207776353537203E-3</v>
       </c>
-      <c r="P26" s="128">
+      <c r="P26" s="103">
         <f>M26*O26</f>
         <v>3.0526893738759699E-2</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B27" s="127" t="s">
+      <c r="B27" s="102" t="s">
         <v>226</v>
       </c>
-      <c r="C27" s="127" t="s">
+      <c r="C27" s="102" t="s">
         <v>227</v>
       </c>
-      <c r="D27" s="127" t="s">
+      <c r="D27" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="127" t="s">
+      <c r="E27" s="102" t="s">
         <v>228</v>
       </c>
-      <c r="F27" s="126" t="s">
+      <c r="F27" s="112" t="s">
         <v>230</v>
       </c>
-      <c r="G27" s="126"/>
-      <c r="H27" s="126"/>
-      <c r="I27" s="126"/>
-      <c r="J27" s="126"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="125"/>
-      <c r="F28" s="125"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="125"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B30" s="5" t="s">
@@ -4265,16 +4251,16 @@
         <v>47</v>
       </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="104" t="s">
+      <c r="F31" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="111"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="111"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="111"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
@@ -4541,11 +4527,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="F31:M31"/>
@@ -4561,6 +4542,11 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="F27:J27"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4580,28 +4566,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104" t="s">
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="110"/>
-      <c r="D3" s="104"/>
+      <c r="B3" s="114"/>
+      <c r="D3" s="111"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -5783,35 +5769,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="118" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="121" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="118" t="s">
+      <c r="D3" s="123" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="114" t="s">
+      <c r="F3" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117" t="s">
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="111" t="s">
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="126"/>
+      <c r="N3" s="115" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="115"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="119"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="124"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -5836,12 +5822,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="112"/>
+      <c r="N4" s="116"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="122"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="125"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -5873,7 +5859,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="113"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6261,35 +6247,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="118" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="121" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="123" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="114" t="s">
+      <c r="F19" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117" t="s">
+      <c r="G19" s="121"/>
+      <c r="H19" s="121"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="121"/>
-      <c r="N19" s="111" t="s">
+      <c r="K19" s="121"/>
+      <c r="L19" s="121"/>
+      <c r="M19" s="126"/>
+      <c r="N19" s="115" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="115"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="119"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="111"/>
+      <c r="D20" s="124"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6314,12 +6300,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="112"/>
+      <c r="N20" s="116"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="116"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="120"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="128"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6351,7 +6337,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="113"/>
+      <c r="N21" s="117"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">
@@ -6849,18 +6835,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3256A65-BFEA-4D43-B402-BF7FE6B8567C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB83A3E-0ED7-4B87-A894-B0C5BFCDAA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="235">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -900,10 +900,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 10ms delay 필요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Duty</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -921,6 +917,26 @@
   </si>
   <si>
     <t>LED 전류 Duty 설정 (1% 단위 조절)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model Select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 or 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 : Model for one XD04, 2 : Model for two XD04s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 최소 10ms delay 필요</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1653,7 +1669,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1967,6 +1983,15 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1979,65 +2004,68 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2077,14 +2105,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>28258</xdr:rowOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>31432</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2127,7 +2155,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2198,7 +2226,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2271,14 +2299,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>28258</xdr:rowOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>31433</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2321,7 +2349,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2392,7 +2420,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2465,13 +2493,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2522,13 +2550,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2579,7 +2607,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2662,7 +2690,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2745,14 +2773,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>28256</xdr:rowOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>31431</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2795,7 +2823,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2866,7 +2894,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2939,13 +2967,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2996,13 +3024,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3053,7 +3081,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3136,7 +3164,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3764,7 +3792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P110"/>
+  <dimension ref="B2:P111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3786,14 +3814,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="105" t="s">
-        <v>225</v>
-      </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
+      <c r="B3" s="108" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3845,14 +3873,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="109" t="s">
+      <c r="E7" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="109"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="109"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3864,14 +3892,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="110" t="s">
+      <c r="E8" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3883,14 +3911,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="109" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="108"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="111"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3902,14 +3930,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="110" t="s">
+      <c r="E10" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3921,14 +3949,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="106" t="s">
+      <c r="E11" s="109" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="107"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107"/>
-      <c r="I11" s="107"/>
-      <c r="J11" s="108"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="111"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3940,14 +3968,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="110" t="s">
+      <c r="E12" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="110"/>
-      <c r="G12" s="110"/>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3959,14 +3987,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="106" t="s">
+      <c r="E13" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="108"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="111"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -3986,13 +4014,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="109" t="s">
+      <c r="F17" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
+      <c r="G17" s="106"/>
+      <c r="H17" s="106"/>
+      <c r="I17" s="106"/>
+      <c r="J17" s="106"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4007,13 +4035,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="110" t="s">
+      <c r="F18" s="105" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4028,13 +4056,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="F19" s="105" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="105"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4049,13 +4077,13 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="110" t="s">
+      <c r="F20" s="105" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4070,13 +4098,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="129" t="s">
-        <v>229</v>
-      </c>
-      <c r="G21" s="129"/>
-      <c r="H21" s="129"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="129"/>
+      <c r="F21" s="105" t="s">
+        <v>228</v>
+      </c>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4091,13 +4119,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="110" t="s">
+      <c r="F22" s="105" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="110"/>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4112,13 +4140,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="110" t="s">
+      <c r="F23" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4133,13 +4161,13 @@
       <c r="E24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F24" s="110" t="s">
+      <c r="F24" s="105" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4154,13 +4182,13 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="110" t="s">
+      <c r="F25" s="105" t="s">
         <v>218</v>
       </c>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
       <c r="L25" s="101" t="s">
         <v>221</v>
       </c>
@@ -4190,13 +4218,13 @@
       <c r="E26" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F26" s="110" t="s">
+      <c r="F26" s="105" t="s">
         <v>220</v>
       </c>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="105"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
@@ -4205,165 +4233,170 @@
         <v>25.006105006105006</v>
       </c>
       <c r="N26" s="6">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O26" s="104">
-        <f>N26/16383</f>
-        <v>1.2207776353537203E-3</v>
+        <f>N26/4095</f>
+        <v>1.221001221001221E-3</v>
       </c>
       <c r="P26" s="103">
         <f>M26*O26</f>
-        <v>3.0526893738759699E-2</v>
+        <v>3.0532484744938956E-2</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B27" s="102" t="s">
+      <c r="B27" s="132" t="s">
+        <v>225</v>
+      </c>
+      <c r="C27" s="132" t="s">
         <v>226</v>
       </c>
-      <c r="C27" s="102" t="s">
+      <c r="D27" s="132" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="132" t="s">
         <v>227</v>
       </c>
-      <c r="D27" s="102" t="s">
+      <c r="F27" s="133" t="s">
+        <v>229</v>
+      </c>
+      <c r="G27" s="133"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="133"/>
+      <c r="J27" s="133"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="102" t="s">
+        <v>230</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="102" t="s">
-        <v>228</v>
-      </c>
-      <c r="F27" s="112" t="s">
-        <v>230</v>
-      </c>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="112"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B30" s="5" t="s">
+      <c r="E28" s="102" t="s">
+        <v>232</v>
+      </c>
+      <c r="F28" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="131"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="O29" s="128"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B31" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B31" s="7" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B32" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="7" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="10"/>
-      <c r="F31" s="111" t="s">
+      <c r="E32" s="10"/>
+      <c r="F32" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="111"/>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="111"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I32" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="K32" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>121</v>
-      </c>
+      <c r="G32" s="107"/>
+      <c r="H32" s="107"/>
+      <c r="I32" s="107"/>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="107"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L33" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M33" s="21" t="s">
-        <v>122</v>
+        <v>36</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B34" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="21" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B35" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
@@ -4376,13 +4409,13 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B36" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
@@ -4395,11 +4428,13 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B37" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C37" s="11"/>
+        <v>29</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="D37" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
@@ -4412,13 +4447,11 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C38" s="11"/>
       <c r="D38" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
@@ -4431,13 +4464,13 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B39" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -4450,13 +4483,13 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -4469,13 +4502,13 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B41" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -4488,13 +4521,13 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B42" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -4505,31 +4538,55 @@
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B45" s="5" t="s">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B43" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B46" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B46" s="6" t="s">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B47" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B78" s="6" t="s">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B79" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B110" s="6" t="s">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B111" s="6" t="s">
         <v>201</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F31:M31"/>
+    <mergeCell ref="F32:M32"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="E12:J12"/>
@@ -4542,11 +4599,7 @@
     <mergeCell ref="F20:J20"/>
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="F27:J27"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F28:J28"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4566,28 +4619,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="113" t="s">
+      <c r="B2" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="111" t="s">
+      <c r="D2" s="107" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111" t="s">
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="114"/>
-      <c r="D3" s="111"/>
+      <c r="B3" s="113"/>
+      <c r="D3" s="107"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -5769,35 +5822,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="118" t="s">
+      <c r="B3" s="117" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="121" t="s">
+      <c r="C3" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="123" t="s">
+      <c r="D3" s="121" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="118" t="s">
+      <c r="F3" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121" t="s">
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="115" t="s">
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="114" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="119"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="124"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="122"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -5822,12 +5875,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="116"/>
+      <c r="N4" s="115"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="120"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="125"/>
+      <c r="B5" s="125"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="127"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -5859,7 +5912,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="117"/>
+      <c r="N5" s="116"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6247,35 +6300,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="117" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="121" t="s">
+      <c r="C19" s="120" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="121" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="118" t="s">
+      <c r="F19" s="117" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121" t="s">
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="121"/>
-      <c r="L19" s="121"/>
-      <c r="M19" s="126"/>
-      <c r="N19" s="115" t="s">
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="124"/>
+      <c r="N19" s="114" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="119"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="124"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="122"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6300,12 +6353,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="116"/>
+      <c r="N20" s="115"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="127"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="128"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="123"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6337,7 +6390,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="117"/>
+      <c r="N21" s="116"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">
@@ -6835,18 +6888,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB83A3E-0ED7-4B87-A894-B0C5BFCDAA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A4AF7F-DF61-4417-B998-CEBFCD93C2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -932,11 +932,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1 : Model for one XD04, 2 : Model for two XD04s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Baudrate = 115200, Parity = None, Stopbits = 1-bit, Data = 8-bits, Protocol 사이 최소 10ms delay 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 : Model for one XD04, 2 : Model for two XD04s, Default Model : two XD04s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1669,7 +1669,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1983,6 +1983,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1992,6 +1995,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2051,24 +2063,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3814,14 +3808,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="108" t="s">
-        <v>234</v>
-      </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="108"/>
+      <c r="B3" s="112" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3873,14 +3867,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="106" t="s">
+      <c r="E7" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3892,14 +3886,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="105" t="s">
+      <c r="E8" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3911,14 +3905,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="109" t="s">
+      <c r="E9" s="113" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="111"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="114"/>
+      <c r="H9" s="114"/>
+      <c r="I9" s="114"/>
+      <c r="J9" s="115"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3930,14 +3924,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="105" t="s">
+      <c r="E10" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3949,14 +3943,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="113" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="110"/>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="111"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="114"/>
+      <c r="I11" s="114"/>
+      <c r="J11" s="115"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3968,14 +3962,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3987,14 +3981,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="109" t="s">
+      <c r="E13" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="111"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="115"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -4014,13 +4008,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4035,13 +4029,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="106" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4056,13 +4050,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="105" t="s">
+      <c r="F19" s="106" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4077,13 +4071,13 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="105" t="s">
+      <c r="F20" s="106" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4098,13 +4092,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="105" t="s">
+      <c r="F21" s="106" t="s">
         <v>228</v>
       </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4119,13 +4113,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="105" t="s">
+      <c r="F22" s="106" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="105"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="106"/>
+      <c r="J22" s="106"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4140,13 +4134,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="105" t="s">
+      <c r="F23" s="106" t="s">
         <v>216</v>
       </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="105"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4161,13 +4155,13 @@
       <c r="E24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F24" s="105" t="s">
+      <c r="F24" s="106" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="106"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4182,13 +4176,13 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="105" t="s">
+      <c r="F25" s="106" t="s">
         <v>218</v>
       </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
       <c r="L25" s="101" t="s">
         <v>221</v>
       </c>
@@ -4218,13 +4212,13 @@
       <c r="E26" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F26" s="105" t="s">
+      <c r="F26" s="106" t="s">
         <v>220</v>
       </c>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="105"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
@@ -4245,25 +4239,25 @@
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B27" s="132" t="s">
+      <c r="B27" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C27" s="132" t="s">
+      <c r="C27" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D27" s="132" t="s">
+      <c r="D27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="132" t="s">
+      <c r="E27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F27" s="133" t="s">
+      <c r="F27" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="106"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B28" s="102" t="s">
@@ -4278,16 +4272,16 @@
       <c r="E28" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="129" t="s">
-        <v>233</v>
-      </c>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="131"/>
+      <c r="F28" s="109" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="111"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="O29" s="128"/>
+      <c r="O29" s="105"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B31" s="5" t="s">
@@ -4303,16 +4297,16 @@
         <v>47</v>
       </c>
       <c r="E32" s="10"/>
-      <c r="F32" s="107" t="s">
+      <c r="F32" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="107"/>
-      <c r="H32" s="107"/>
-      <c r="I32" s="107"/>
-      <c r="J32" s="107"/>
-      <c r="K32" s="107"/>
-      <c r="L32" s="107"/>
-      <c r="M32" s="107"/>
+      <c r="G32" s="108"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="108"/>
+      <c r="J32" s="108"/>
+      <c r="K32" s="108"/>
+      <c r="L32" s="108"/>
+      <c r="M32" s="108"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B33" s="8" t="s">
@@ -4619,28 +4613,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="D2" s="108" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="107" t="s">
+      <c r="E2" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107" t="s">
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="113"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="D3" s="108"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -5822,35 +5816,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="117" t="s">
+      <c r="B3" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="120" t="s">
+      <c r="C3" s="124" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="121" t="s">
+      <c r="D3" s="125" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120" t="s">
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="114" t="s">
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="118" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="118"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="122"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="126"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -5875,12 +5869,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="115"/>
+      <c r="N4" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="125"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="127"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="131"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -5912,7 +5906,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="116"/>
+      <c r="N5" s="120"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6300,35 +6294,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="124" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="121" t="s">
+      <c r="D19" s="125" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="117" t="s">
+      <c r="F19" s="121" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="120"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="120"/>
-      <c r="J19" s="120" t="s">
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="124" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="120"/>
-      <c r="L19" s="120"/>
-      <c r="M19" s="124"/>
-      <c r="N19" s="114" t="s">
+      <c r="K19" s="124"/>
+      <c r="L19" s="124"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="118" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="118"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="122"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="126"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6353,12 +6347,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="115"/>
+      <c r="N20" s="119"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="119"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="123"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="127"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6390,7 +6384,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="116"/>
+      <c r="N21" s="120"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A4AF7F-DF61-4417-B998-CEBFCD93C2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1862D149-21F0-4537-972E-4F1A439E58CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71835" yWindow="2115" windowWidth="29130" windowHeight="15810" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="B'D check list" sheetId="3" r:id="rId3"/>
     <sheet name="B'D connector summary" sheetId="5" r:id="rId4"/>
     <sheet name="example" sheetId="6" r:id="rId5"/>
+    <sheet name="Protocol Sequnece for Test" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="258">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -936,7 +937,105 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1 : Model for one XD04, 2 : Model for two XD04s, Default Model : two XD04s</t>
+    <t>Test CH Dependency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test SCAN No.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Line Delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xA2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Test CH Dependency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Test SCAN No.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Test Line Delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Protocol Sequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>To Do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Compare the LED brightness between all LEDs on and individual LEDs on. 
+2. No brightness difference is allowed between the two conditions.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. The brightness must be maintained without any variation.
+2. OFF or low brightness for more than 0.5 seconds is considered a defect.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. There is no history of this type of defect occurring. (26.04.20)
+2. After 17s, test is stopped.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Minor flicker is a transient effect caused by line delay switching.
+2. After 7s, test is stopped.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. There is no history of this type of defect occurring. (26.04.20)
+2. After 25s, test is stopped.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 : Model for one XD04, 2 : Model for two XD04s, Default Model : two XD04s / Test Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Test Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Above 3-test items include Test Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. If a daisy I/O issue occurs, the bar is set to the OFF state.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test CH Dependency + Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test SCAN No. + Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test Line Delay + Daisy I/O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. The pattern is 1.0s ON → 0.1s OFF, repeated 8-times. 
+2. No brightness difference is allowed between ON-OFF cycles.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -949,7 +1048,7 @@
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
     <numFmt numFmtId="178" formatCode="0.000&quot;mA&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1015,6 +1114,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1669,7 +1777,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1986,9 +2094,39 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2004,64 +2142,70 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2099,14 +2243,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>31432</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2149,7 +2293,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2220,7 +2364,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2293,14 +2437,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>31433</xdr:rowOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2343,7 +2487,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2414,7 +2558,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2487,13 +2631,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2544,13 +2688,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2601,7 +2745,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2684,7 +2828,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2767,14 +2911,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>140</xdr:row>
-      <xdr:rowOff>31431</xdr:rowOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>28256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2817,7 +2961,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2888,7 +3032,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2961,13 +3105,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3018,13 +3162,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3075,7 +3219,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3158,7 +3302,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3786,7 +3930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P111"/>
+  <dimension ref="B2:P115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
@@ -3808,14 +3952,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="113" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -3867,14 +4011,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="107" t="s">
+      <c r="E7" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -3886,14 +4030,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="106" t="s">
+      <c r="E8" s="112" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="106"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -3905,14 +4049,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="113" t="s">
+      <c r="E9" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="114"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="116"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -3924,14 +4068,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="106" t="s">
+      <c r="E10" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -3943,14 +4087,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="114" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="114"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
-      <c r="J11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="116"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -3962,14 +4106,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="106" t="s">
+      <c r="E12" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -3981,14 +4125,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="113" t="s">
+      <c r="E13" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="114"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="114"/>
-      <c r="I13" s="114"/>
-      <c r="J13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="116"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -4008,13 +4152,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="107" t="s">
+      <c r="F17" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="107"/>
-      <c r="H17" s="107"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="107"/>
+      <c r="G17" s="117"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="117"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4029,13 +4173,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="106" t="s">
+      <c r="F18" s="112" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="112"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4050,13 +4194,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="106" t="s">
+      <c r="F19" s="112" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4071,13 +4215,13 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="106" t="s">
+      <c r="F20" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="106"/>
-      <c r="H20" s="106"/>
-      <c r="I20" s="106"/>
-      <c r="J20" s="106"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
+      <c r="J20" s="112"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
@@ -4092,13 +4236,13 @@
       <c r="E21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="106" t="s">
+      <c r="F21" s="112" t="s">
         <v>228</v>
       </c>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4113,13 +4257,13 @@
       <c r="E22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="106" t="s">
+      <c r="F22" s="112" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="106"/>
-      <c r="H22" s="106"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="106"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="112"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4134,13 +4278,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="106" t="s">
+      <c r="F23" s="112" t="s">
         <v>216</v>
       </c>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4155,13 +4299,13 @@
       <c r="E24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F24" s="106" t="s">
+      <c r="F24" s="112" t="s">
         <v>217</v>
       </c>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="106"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4176,13 +4320,13 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="106" t="s">
+      <c r="F25" s="112" t="s">
         <v>218</v>
       </c>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
       <c r="L25" s="101" t="s">
         <v>221</v>
       </c>
@@ -4212,13 +4356,13 @@
       <c r="E26" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="112" t="s">
         <v>220</v>
       </c>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-      <c r="I26" s="106"/>
-      <c r="J26" s="106"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
       <c r="L26" s="6">
         <v>800</v>
       </c>
@@ -4251,13 +4395,13 @@
       <c r="E27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F27" s="106" t="s">
+      <c r="F27" s="112" t="s">
         <v>229</v>
       </c>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B28" s="102" t="s">
@@ -4272,199 +4416,194 @@
       <c r="E28" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="109" t="s">
+      <c r="F28" s="119" t="s">
+        <v>250</v>
+      </c>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="120"/>
+      <c r="J28" s="121"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B29" s="102" t="s">
         <v>234</v>
       </c>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="111"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="C29" s="102" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="102" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="102">
+        <v>0</v>
+      </c>
+      <c r="F29" s="141" t="s">
+        <v>254</v>
+      </c>
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
       <c r="O29" s="105"/>
     </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B30" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="C30" s="102" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30" s="102" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="102" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="119" t="s">
+        <v>255</v>
+      </c>
+      <c r="G30" s="120"/>
+      <c r="H30" s="120"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="O30" s="105"/>
+    </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="102" t="s">
+        <v>238</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="102" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="102" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="119" t="s">
+        <v>256</v>
+      </c>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="121"/>
+      <c r="O31" s="105"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="O32" s="105"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="O33" s="105"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B35" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B32" s="7" t="s">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B36" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="7" t="s">
+      <c r="C36" s="9"/>
+      <c r="D36" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="108" t="s">
+      <c r="E36" s="10"/>
+      <c r="F36" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="G32" s="108"/>
-      <c r="H32" s="108"/>
-      <c r="I32" s="108"/>
-      <c r="J32" s="108"/>
-      <c r="K32" s="108"/>
-      <c r="L32" s="108"/>
-      <c r="M32" s="108"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B33" s="8" t="s">
+      <c r="G36" s="118"/>
+      <c r="H36" s="118"/>
+      <c r="I36" s="118"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="118"/>
+      <c r="M36" s="118"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B37" s="8" t="s">
         <v>25</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="K33" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B34" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="K34" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B36" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B37" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="11"/>
+        <v>26</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="D38" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+      <c r="E38" s="17"/>
+      <c r="F38" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B39" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
@@ -4475,15 +4614,15 @@
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -4494,15 +4633,15 @@
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B41" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -4513,15 +4652,13 @@
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B42" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C42" s="11"/>
       <c r="D42" s="8" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -4532,15 +4669,15 @@
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B43" s="8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
@@ -4551,36 +4688,105 @@
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B46" s="5" t="s">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B44" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B45" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B47" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B47" s="6" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B79" s="6" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B83" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B111" s="6" t="s">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B115" s="6" t="s">
         <v>201</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F32:M32"/>
+  <mergeCells count="24">
+    <mergeCell ref="F36:M36"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="E12:J12"/>
@@ -4594,6 +4800,16 @@
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="F28:J28"/>
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="E7:J7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4613,28 +4829,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="122" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="118" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108" t="s">
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="117"/>
-      <c r="D3" s="108"/>
+      <c r="B3" s="123"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -5816,35 +6032,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="124" t="s">
+      <c r="C3" s="130" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="125" t="s">
+      <c r="D3" s="132" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="121" t="s">
+      <c r="F3" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124" t="s">
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="128"/>
-      <c r="N3" s="118" t="s">
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="124" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="122"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="126"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="133"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -5869,12 +6085,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="119"/>
+      <c r="N4" s="125"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B5" s="129"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="131"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="134"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -5906,7 +6122,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="120"/>
+      <c r="N5" s="126"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6294,35 +6510,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="121" t="s">
+      <c r="B19" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="124" t="s">
+      <c r="C19" s="130" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="125" t="s">
+      <c r="D19" s="132" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="121" t="s">
+      <c r="F19" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="124"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="124"/>
-      <c r="J19" s="124" t="s">
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="124"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="118" t="s">
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="135"/>
+      <c r="N19" s="124" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="122"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="126"/>
+      <c r="B20" s="128"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="133"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6347,12 +6563,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="119"/>
+      <c r="N20" s="125"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="123"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="127"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="137"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6384,7 +6600,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="120"/>
+      <c r="N21" s="126"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">
@@ -6882,21 +7098,181 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="J19:M19"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="J19:M19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5FF699-A806-4B4F-BD4A-46DB7B317480}">
+  <dimension ref="B2:L21"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" style="109" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" style="109" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="109" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.75" style="109" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.25" style="109" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.58203125" style="109" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="109"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B2" s="110" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="109" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" s="106" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" s="108" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B6" s="138" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="69">
+        <v>0</v>
+      </c>
+      <c r="D6" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="140" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="109" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" s="106" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B11" s="138" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="69">
+        <v>0</v>
+      </c>
+      <c r="D11" s="139" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="140" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="L12"/>
+    </row>
+    <row r="14" spans="2:12" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="109" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" s="106" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="108" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B16" s="138" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="69">
+        <v>0</v>
+      </c>
+      <c r="D16" s="139" t="s">
+        <v>246</v>
+      </c>
+      <c r="E16" s="140" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B19" s="109" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="106" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="107" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="107" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="108" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="142" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="143" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="139" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" s="140" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1862D149-21F0-4537-972E-4F1A439E58CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CDD45-79C1-4312-A43C-9CC92BD37CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="2115" windowWidth="29130" windowHeight="15810" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
-    <sheet name="xc xd mapping" sheetId="2" r:id="rId2"/>
-    <sheet name="B'D check list" sheetId="3" r:id="rId3"/>
-    <sheet name="B'D connector summary" sheetId="5" r:id="rId4"/>
-    <sheet name="example" sheetId="6" r:id="rId5"/>
-    <sheet name="Protocol Sequnece for Test" sheetId="7" r:id="rId6"/>
+    <sheet name="version" sheetId="8" r:id="rId2"/>
+    <sheet name="xc xd mapping" sheetId="2" r:id="rId3"/>
+    <sheet name="B'D check list" sheetId="3" r:id="rId4"/>
+    <sheet name="B'D connector summary" sheetId="5" r:id="rId5"/>
+    <sheet name="example" sheetId="6" r:id="rId6"/>
+    <sheet name="Protocol Sequnece for Test" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="267">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1036,6 +1037,42 @@
   <si>
     <t>1. The pattern is 1.0s ON → 0.1s OFF, repeated 8-times. 
 2. No brightness difference is allowed between ON-OFF cycles.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0xF1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>version 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Release 날짜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version Code</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 06. 11</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260611.hex</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1048,7 +1085,7 @@
     <numFmt numFmtId="177" formatCode="&quot;Blk-&quot;0"/>
     <numFmt numFmtId="178" formatCode="0.000&quot;mA&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1123,6 +1160,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1777,7 +1829,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2112,27 +2164,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2142,6 +2215,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2188,24 +2264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2243,14 +2301,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>28257</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>28256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2293,7 +2351,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2364,7 +2422,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2437,13 +2495,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2487,7 +2545,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -2558,7 +2616,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -2631,13 +2689,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2688,13 +2746,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1590675</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2745,7 +2803,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -2828,7 +2886,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>537156</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -2911,14 +2969,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>28256</xdr:rowOff>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>28257</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2961,7 +3019,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="572849" cy="280205"/>
@@ -3032,7 +3090,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="497059" cy="280205"/>
@@ -3105,13 +3163,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3162,13 +3220,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1581150</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -3219,7 +3277,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="701282" cy="436786"/>
@@ -3302,7 +3360,7 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>527629</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1093826" cy="436786"/>
@@ -3930,14 +3988,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P115"/>
+  <dimension ref="B2:P116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="18.58203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="7" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="6" customWidth="1"/>
     <col min="6" max="10" width="23.5" style="6" customWidth="1"/>
     <col min="11" max="13" width="10.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="6" customWidth="1"/>
@@ -3952,14 +4010,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="113"/>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="113"/>
-      <c r="G3" s="113"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -4011,14 +4069,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="117" t="s">
+      <c r="E7" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="117"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -4030,14 +4088,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="112" t="s">
+      <c r="E8" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="112"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="125"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -4049,14 +4107,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="114" t="s">
+      <c r="E9" s="120" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="116"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="122"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -4068,14 +4126,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="112" t="s">
+      <c r="E10" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -4087,14 +4145,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="114" t="s">
+      <c r="E11" s="120" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="122"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -4106,14 +4164,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="112" t="s">
+      <c r="E12" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="112"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="125"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -4125,14 +4183,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="114" t="s">
+      <c r="E13" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121"/>
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="122"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -4152,13 +4210,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="117" t="s">
+      <c r="F17" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="124"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4173,13 +4231,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="112" t="s">
+      <c r="F18" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="112"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="112"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="125"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4194,13 +4252,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="112" t="s">
+      <c r="F19" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="125"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4215,62 +4273,60 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="112" t="s">
+      <c r="F20" s="125" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="112"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B21" s="102" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="102" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="112" t="s">
-        <v>228</v>
-      </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="112"/>
+      <c r="E21" s="102" t="s">
+        <v>259</v>
+      </c>
+      <c r="F21" s="126"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="128"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="112" t="s">
-        <v>215</v>
-      </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="112"/>
+        <v>67</v>
+      </c>
+      <c r="F22" s="125" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="125"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>6</v>
@@ -4278,41 +4334,41 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="112" t="s">
-        <v>216</v>
-      </c>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112"/>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
+      <c r="F23" s="125" t="s">
+        <v>215</v>
+      </c>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F24" s="112" t="s">
-        <v>217</v>
-      </c>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
+        <v>68</v>
+      </c>
+      <c r="F24" s="125" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>6</v>
@@ -4320,309 +4376,311 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="112" t="s">
-        <v>218</v>
-      </c>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="L25" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="M25" s="101" t="s">
-        <v>219</v>
-      </c>
-      <c r="N25" s="101" t="s">
-        <v>222</v>
-      </c>
-      <c r="O25" s="101" t="s">
-        <v>224</v>
-      </c>
-      <c r="P25" s="101" t="s">
-        <v>223</v>
-      </c>
+      <c r="F25" s="125" t="s">
+        <v>217</v>
+      </c>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
-        <v>211</v>
+        <v>23</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>212</v>
+        <v>24</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="F26" s="112" t="s">
-        <v>220</v>
-      </c>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="L26" s="6">
-        <v>800</v>
-      </c>
-      <c r="M26" s="103">
-        <f>L26/4095*128</f>
-        <v>25.006105006105006</v>
-      </c>
-      <c r="N26" s="6">
-        <v>5</v>
-      </c>
-      <c r="O26" s="104">
-        <f>N26/4095</f>
-        <v>1.221001221001221E-3</v>
-      </c>
-      <c r="P26" s="103">
-        <f>M26*O26</f>
-        <v>3.0532484744938956E-2</v>
+        <v>120</v>
+      </c>
+      <c r="F26" s="125" t="s">
+        <v>218</v>
+      </c>
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="125"/>
+      <c r="J26" s="125"/>
+      <c r="L26" s="101" t="s">
+        <v>221</v>
+      </c>
+      <c r="M26" s="101" t="s">
+        <v>219</v>
+      </c>
+      <c r="N26" s="101" t="s">
+        <v>222</v>
+      </c>
+      <c r="O26" s="101" t="s">
+        <v>224</v>
+      </c>
+      <c r="P26" s="101" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B27" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F27" s="125" t="s">
+        <v>220</v>
+      </c>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="125"/>
+      <c r="J27" s="125"/>
+      <c r="L27" s="6">
+        <v>800</v>
+      </c>
+      <c r="M27" s="103">
+        <f>L27/4095*128</f>
+        <v>25.006105006105006</v>
+      </c>
+      <c r="N27" s="6">
+        <v>5</v>
+      </c>
+      <c r="O27" s="104">
+        <f>N27/4095</f>
+        <v>1.221001221001221E-3</v>
+      </c>
+      <c r="P27" s="103">
+        <f>M27*O27</f>
+        <v>3.0532484744938956E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F27" s="112" t="s">
+      <c r="F28" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="112"/>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B28" s="102" t="s">
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="125"/>
+      <c r="J28" s="125"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="102" t="s">
+      <c r="C29" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D28" s="102" t="s">
+      <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="102" t="s">
+      <c r="E29" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F28" s="119" t="s">
+      <c r="F29" s="120" t="s">
         <v>250</v>
       </c>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120"/>
-      <c r="J28" s="121"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B29" s="102" t="s">
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="122"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B30" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C29" s="102" t="s">
+      <c r="C30" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="102" t="s">
+      <c r="D30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="102">
-        <v>0</v>
-      </c>
-      <c r="F29" s="141" t="s">
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+      <c r="F30" s="125" t="s">
         <v>254</v>
       </c>
-      <c r="G29" s="141"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="O29" s="105"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B30" s="102" t="s">
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="O30" s="105"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B31" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C30" s="102" t="s">
+      <c r="C31" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="102" t="s">
+      <c r="D31" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="102" t="s">
+      <c r="E31" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F30" s="119" t="s">
+      <c r="F31" s="120" t="s">
         <v>255</v>
       </c>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="121"/>
-      <c r="O30" s="105"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B31" s="102" t="s">
+      <c r="G31" s="121"/>
+      <c r="H31" s="121"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="122"/>
+      <c r="O31" s="105"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B32" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C31" s="102" t="s">
+      <c r="C32" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D31" s="102" t="s">
+      <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="102" t="s">
+      <c r="E32" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="119" t="s">
+      <c r="F32" s="120" t="s">
         <v>256</v>
       </c>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="121"/>
-      <c r="O31" s="105"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="G32" s="121"/>
+      <c r="H32" s="121"/>
+      <c r="I32" s="121"/>
+      <c r="J32" s="122"/>
       <c r="O32" s="105"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="O33" s="105"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B35" s="5" t="s">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="O34" s="105"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B36" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B36" s="7" t="s">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B37" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="7" t="s">
+      <c r="C37" s="9"/>
+      <c r="D37" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="118" t="s">
+      <c r="E37" s="10"/>
+      <c r="F37" s="129" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
-      <c r="M36" s="118"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B37" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="L37" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="M37" s="16" t="s">
-        <v>121</v>
-      </c>
+      <c r="G37" s="129"/>
+      <c r="H37" s="129"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="129"/>
+      <c r="K37" s="129"/>
+      <c r="L37" s="129"/>
+      <c r="M37" s="129"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M38" s="21" t="s">
-        <v>122</v>
+        <v>36</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B39" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="E39" s="17"/>
+      <c r="F39" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="M39" s="21" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E40" s="9"/>
       <c r="F40" s="9"/>
@@ -4635,13 +4693,13 @@
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B41" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
@@ -4654,11 +4712,13 @@
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B42" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="11"/>
+        <v>29</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="D42" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
@@ -4671,13 +4731,11 @@
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B43" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C43" s="11"/>
       <c r="D43" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
@@ -4690,13 +4748,13 @@
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B44" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
@@ -4709,13 +4767,13 @@
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B45" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
@@ -4728,13 +4786,13 @@
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B46" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
@@ -4747,13 +4805,13 @@
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B47" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>46</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E47" s="9"/>
       <c r="F47" s="9"/>
@@ -4764,60 +4822,130 @@
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" s="5" t="s">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B48" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B51" s="6" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" s="6" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B83" s="6" t="s">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B84" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B115" s="6" t="s">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B116" s="6" t="s">
         <v>201</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="F36:M36"/>
+  <mergeCells count="25">
+    <mergeCell ref="F37:M37"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
     <mergeCell ref="E12:J12"/>
+    <mergeCell ref="F25:J25"/>
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="F23:J23"/>
     <mergeCell ref="F22:J22"/>
-    <mergeCell ref="F21:J21"/>
     <mergeCell ref="F19:J19"/>
     <mergeCell ref="F18:J18"/>
     <mergeCell ref="F20:J20"/>
-    <mergeCell ref="F26:J26"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="F28:J28"/>
+    <mergeCell ref="F29:J29"/>
+    <mergeCell ref="F32:J32"/>
+    <mergeCell ref="F30:J30"/>
     <mergeCell ref="F31:J31"/>
-    <mergeCell ref="F29:J29"/>
-    <mergeCell ref="F30:J30"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="E9:J9"/>
     <mergeCell ref="E11:J11"/>
     <mergeCell ref="E13:J13"/>
     <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F26:J26"/>
     <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F21:J21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02792469-EFBA-4F9A-B5A0-1744FB4929FB}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="B2:E3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B2" s="117" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="117" t="s">
+        <v>261</v>
+      </c>
+      <c r="D2" s="117" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="117" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="118">
+        <v>1</v>
+      </c>
+      <c r="C3" s="119" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="119" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="119">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CADB1EA6-99AD-4FE8-82D9-732EE4C0DA8F}">
   <dimension ref="B2:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
@@ -4829,28 +4957,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="122" t="s">
+      <c r="B2" s="130" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="118" t="s">
+      <c r="D2" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="118" t="s">
+      <c r="E2" s="129" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118" t="s">
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="123"/>
-      <c r="D3" s="118"/>
+      <c r="B3" s="131"/>
+      <c r="D3" s="129"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -5729,7 +5857,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5776C9-E522-4127-B982-E334D5A025FE}">
   <dimension ref="B1:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -5985,7 +6113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1D2CDE-03D0-4073-94E8-BF70397D701B}">
   <dimension ref="B2:W2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -6011,7 +6139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A57173FD-D29F-465B-B16F-5A3BAEE50DB9}">
   <dimension ref="B2:N34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.45"/>
@@ -6032,35 +6160,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="132" t="s">
+      <c r="D3" s="140" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="127" t="s">
+      <c r="F3" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130" t="s">
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="124" t="s">
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="132" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="128"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="133"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="141"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -6085,12 +6213,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="125"/>
+      <c r="N4" s="133"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="129"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="134"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="142"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -6122,7 +6250,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="126"/>
+      <c r="N5" s="134"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6510,35 +6638,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="135" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="138" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="132" t="s">
+      <c r="D19" s="140" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="127" t="s">
+      <c r="F19" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130" t="s">
+      <c r="G19" s="138"/>
+      <c r="H19" s="138"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="138" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="130"/>
-      <c r="L19" s="130"/>
-      <c r="M19" s="135"/>
-      <c r="N19" s="124" t="s">
+      <c r="K19" s="138"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="143"/>
+      <c r="N19" s="132" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="128"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="133"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="141"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6563,12 +6691,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="125"/>
+      <c r="N20" s="133"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="136"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="137"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="145"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6600,7 +6728,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="126"/>
+      <c r="N21" s="134"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">
@@ -7117,7 +7245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5FF699-A806-4B4F-BD4A-46DB7B317480}">
   <dimension ref="B2:L21"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -7156,7 +7284,7 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="112" t="s">
         <v>234</v>
       </c>
       <c r="C6" s="69">
@@ -7165,7 +7293,7 @@
       <c r="D6" s="111" t="s">
         <v>245</v>
       </c>
-      <c r="E6" s="140" t="s">
+      <c r="E6" s="114" t="s">
         <v>249</v>
       </c>
     </row>
@@ -7189,16 +7317,16 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="138" t="s">
+      <c r="B11" s="112" t="s">
         <v>236</v>
       </c>
       <c r="C11" s="69">
         <v>0</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="113" t="s">
         <v>257</v>
       </c>
-      <c r="E11" s="140" t="s">
+      <c r="E11" s="114" t="s">
         <v>247</v>
       </c>
     </row>
@@ -7225,16 +7353,16 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="34.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="112" t="s">
         <v>238</v>
       </c>
       <c r="C16" s="69">
         <v>0</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="113" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="140" t="s">
+      <c r="E16" s="114" t="s">
         <v>248</v>
       </c>
     </row>
@@ -7258,16 +7386,16 @@
       </c>
     </row>
     <row r="21" spans="2:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="142" t="s">
+      <c r="B21" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="143" t="s">
+      <c r="C21" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="139" t="s">
+      <c r="D21" s="113" t="s">
         <v>253</v>
       </c>
-      <c r="E21" s="140" t="s">
+      <c r="E21" s="114" t="s">
         <v>252</v>
       </c>
     </row>

--- a/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
+++ b/X-Series/XD04P/LED_Module_Control_BD/XD04_LED_Module_Control_BD/Docs/xdic_led_module_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD04P\LED_Module_Control_BD\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592CDD45-79C1-4312-A43C-9CC92BD37CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18EF96-483F-472E-B8C7-4B3D0FF4D70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="protocol" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="example" sheetId="6" r:id="rId6"/>
     <sheet name="Protocol Sequnece for Test" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="270">
   <si>
     <t>SOP</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1074,6 +1074,18 @@
   <si>
     <t>Version</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"26. 07. 07</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260707_XD_S.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260707_XD_D.hex</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1176,7 +1188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,6 +1225,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="47">
     <border>
@@ -1829,7 +1847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2188,6 +2206,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2203,21 +2236,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2239,31 +2266,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4010,14 +4037,14 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="123" t="s">
+      <c r="B3" s="128" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
@@ -4069,14 +4096,14 @@
       <c r="D7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="124" t="s">
+      <c r="E7" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
@@ -4088,14 +4115,14 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="125" t="s">
+      <c r="E8" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
@@ -4107,14 +4134,14 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="125" t="s">
         <v>168</v>
       </c>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="126"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="127"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
@@ -4126,14 +4153,14 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="125" t="s">
+      <c r="E10" s="124" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="125"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="124"/>
+      <c r="J10" s="124"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" s="2" t="s">
@@ -4145,14 +4172,14 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="120" t="s">
+      <c r="E11" s="125" t="s">
         <v>214</v>
       </c>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="122"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
@@ -4164,14 +4191,14 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="125" t="s">
+      <c r="E12" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
@@ -4183,14 +4210,14 @@
       <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="120" t="s">
+      <c r="E13" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="122"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="126"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="127"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
@@ -4210,13 +4237,13 @@
       <c r="E17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="124" t="s">
+      <c r="F17" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="124"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="129"/>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B18" s="3" t="s">
@@ -4231,13 +4258,13 @@
       <c r="E18" s="4">
         <v>0</v>
       </c>
-      <c r="F18" s="125" t="s">
+      <c r="F18" s="124" t="s">
         <v>203</v>
       </c>
-      <c r="G18" s="125"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="125"/>
-      <c r="J18" s="125"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
@@ -4252,13 +4279,13 @@
       <c r="E19" s="4">
         <v>0</v>
       </c>
-      <c r="F19" s="125" t="s">
+      <c r="F19" s="124" t="s">
         <v>198</v>
       </c>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="124"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B20" s="3" t="s">
@@ -4273,32 +4300,32 @@
       <c r="E20" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F20" s="125" t="s">
+      <c r="F20" s="124" t="s">
         <v>119</v>
       </c>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.45">
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="122" t="s">
         <v>266</v>
       </c>
-      <c r="C21" s="102" t="s">
+      <c r="C21" s="122" t="s">
         <v>258</v>
       </c>
-      <c r="D21" s="102" t="s">
+      <c r="D21" s="122" t="s">
         <v>5</v>
       </c>
       <c r="E21" s="102" t="s">
         <v>259</v>
       </c>
-      <c r="F21" s="126"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="128"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
+      <c r="J21" s="132"/>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
@@ -4313,13 +4340,13 @@
       <c r="E22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="125" t="s">
+      <c r="F22" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="124"/>
+      <c r="J22" s="124"/>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B23" s="3" t="s">
@@ -4334,13 +4361,13 @@
       <c r="E23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F23" s="125" t="s">
+      <c r="F23" s="124" t="s">
         <v>215</v>
       </c>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="124"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
@@ -4355,13 +4382,13 @@
       <c r="E24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="125" t="s">
+      <c r="F24" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="124"/>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B25" s="3" t="s">
@@ -4376,13 +4403,13 @@
       <c r="E25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="125" t="s">
+      <c r="F25" s="124" t="s">
         <v>217</v>
       </c>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
+      <c r="I25" s="124"/>
+      <c r="J25" s="124"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B26" s="3" t="s">
@@ -4397,13 +4424,13 @@
       <c r="E26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="125" t="s">
+      <c r="F26" s="124" t="s">
         <v>218</v>
       </c>
-      <c r="G26" s="125"/>
-      <c r="H26" s="125"/>
-      <c r="I26" s="125"/>
-      <c r="J26" s="125"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
       <c r="L26" s="101" t="s">
         <v>221</v>
       </c>
@@ -4433,13 +4460,13 @@
       <c r="E27" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F27" s="125" t="s">
+      <c r="F27" s="124" t="s">
         <v>220</v>
       </c>
-      <c r="G27" s="125"/>
-      <c r="H27" s="125"/>
-      <c r="I27" s="125"/>
-      <c r="J27" s="125"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="124"/>
       <c r="L27" s="6">
         <v>800</v>
       </c>
@@ -4472,13 +4499,13 @@
       <c r="E28" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F28" s="125" t="s">
+      <c r="F28" s="124" t="s">
         <v>229</v>
       </c>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="125"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="124"/>
+      <c r="J28" s="124"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
@@ -4493,13 +4520,13 @@
       <c r="E29" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="F29" s="120" t="s">
+      <c r="F29" s="125" t="s">
         <v>250</v>
       </c>
-      <c r="G29" s="121"/>
-      <c r="H29" s="121"/>
-      <c r="I29" s="121"/>
-      <c r="J29" s="122"/>
+      <c r="G29" s="126"/>
+      <c r="H29" s="126"/>
+      <c r="I29" s="126"/>
+      <c r="J29" s="127"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.45">
       <c r="B30" s="3" t="s">
@@ -4514,13 +4541,13 @@
       <c r="E30" s="3">
         <v>0</v>
       </c>
-      <c r="F30" s="125" t="s">
+      <c r="F30" s="124" t="s">
         <v>254</v>
       </c>
-      <c r="G30" s="125"/>
-      <c r="H30" s="125"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="125"/>
+      <c r="G30" s="124"/>
+      <c r="H30" s="124"/>
+      <c r="I30" s="124"/>
+      <c r="J30" s="124"/>
       <c r="O30" s="105"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.45">
@@ -4536,13 +4563,13 @@
       <c r="E31" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F31" s="120" t="s">
+      <c r="F31" s="125" t="s">
         <v>255</v>
       </c>
-      <c r="G31" s="121"/>
-      <c r="H31" s="121"/>
-      <c r="I31" s="121"/>
-      <c r="J31" s="122"/>
+      <c r="G31" s="126"/>
+      <c r="H31" s="126"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="127"/>
       <c r="O31" s="105"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.45">
@@ -4558,13 +4585,13 @@
       <c r="E32" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F32" s="120" t="s">
+      <c r="F32" s="125" t="s">
         <v>256</v>
       </c>
-      <c r="G32" s="121"/>
-      <c r="H32" s="121"/>
-      <c r="I32" s="121"/>
-      <c r="J32" s="122"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="126"/>
+      <c r="I32" s="126"/>
+      <c r="J32" s="127"/>
       <c r="O32" s="105"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -4587,16 +4614,16 @@
         <v>47</v>
       </c>
       <c r="E37" s="10"/>
-      <c r="F37" s="129" t="s">
+      <c r="F37" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="129"/>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="L37" s="129"/>
-      <c r="M37" s="129"/>
+      <c r="G37" s="123"/>
+      <c r="H37" s="123"/>
+      <c r="I37" s="123"/>
+      <c r="J37" s="123"/>
+      <c r="K37" s="123"/>
+      <c r="L37" s="123"/>
+      <c r="M37" s="123"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
@@ -4863,6 +4890,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F31:J31"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="F26:J26"/>
+    <mergeCell ref="E7:J7"/>
+    <mergeCell ref="F21:J21"/>
     <mergeCell ref="F37:M37"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="E10:J10"/>
@@ -4879,15 +4915,6 @@
     <mergeCell ref="F29:J29"/>
     <mergeCell ref="F32:J32"/>
     <mergeCell ref="F30:J30"/>
-    <mergeCell ref="F31:J31"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="E9:J9"/>
-    <mergeCell ref="E11:J11"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="E7:J7"/>
-    <mergeCell ref="F21:J21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4901,7 +4928,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="B2:E3"/>
+  <dimension ref="B2:E5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -4937,6 +4964,34 @@
       </c>
       <c r="E3" s="119">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="120">
+        <v>2</v>
+      </c>
+      <c r="C4" s="121" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="121" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="120">
+        <v>3</v>
+      </c>
+      <c r="C5" s="121" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="121" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="121">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4957,28 +5012,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="129" t="s">
+      <c r="D2" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="129" t="s">
+      <c r="E2" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129" t="s">
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B3" s="131"/>
-      <c r="D3" s="129"/>
+      <c r="B3" s="134"/>
+      <c r="D3" s="123"/>
       <c r="E3" s="7" t="s">
         <v>112</v>
       </c>
@@ -6160,35 +6215,35 @@
       </c>
     </row>
     <row r="3" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="138" t="s">
+      <c r="C3" s="141" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="140" t="s">
+      <c r="D3" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="135" t="s">
+      <c r="F3" s="138" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138" t="s">
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="132" t="s">
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="135" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="136"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="141"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="123"/>
+      <c r="D4" s="143"/>
       <c r="F4" s="60" t="s">
         <v>112</v>
       </c>
@@ -6213,12 +6268,12 @@
       <c r="M4" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N4" s="133"/>
+      <c r="N4" s="136"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B5" s="137"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="142"/>
+      <c r="B5" s="146"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="148"/>
       <c r="F5" s="70">
         <v>1</v>
       </c>
@@ -6250,7 +6305,7 @@
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="N5" s="134"/>
+      <c r="N5" s="137"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B6" s="66">
@@ -6638,35 +6693,35 @@
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B19" s="135" t="s">
+      <c r="B19" s="138" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="138" t="s">
+      <c r="C19" s="141" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="140" t="s">
+      <c r="D19" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="F19" s="135" t="s">
+      <c r="F19" s="138" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="138"/>
-      <c r="H19" s="138"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="138" t="s">
+      <c r="G19" s="141"/>
+      <c r="H19" s="141"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="143"/>
-      <c r="N19" s="132" t="s">
+      <c r="K19" s="141"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="145"/>
+      <c r="N19" s="135" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B20" s="136"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="141"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="143"/>
       <c r="F20" s="60" t="s">
         <v>112</v>
       </c>
@@ -6691,12 +6746,12 @@
       <c r="M20" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="N20" s="133"/>
+      <c r="N20" s="136"/>
     </row>
     <row r="21" spans="2:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="144"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="145"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="144"/>
       <c r="F21" s="90">
         <v>12</v>
       </c>
@@ -6728,7 +6783,7 @@
         <f t="shared" ref="M21" si="7">L21+20</f>
         <v>152</v>
       </c>
-      <c r="N21" s="134"/>
+      <c r="N21" s="137"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="85">
@@ -7226,18 +7281,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
     <mergeCell ref="N19:N21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="D19:D21"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
